--- a/data/export/shortlist_noncs.xlsx
+++ b/data/export/shortlist_noncs.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shortlist" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$N$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$N$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -517,32 +517,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>agents</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Harikesh S. Wong</t>
+          <t>Weijing Tang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biology, Core Member, Ragon Institute Education</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>wongs@mit.edu</t>
+          <t>weijingt@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -552,14 +556,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>computational modelling; quantitative fluorescence microscopy; intercellular circuits</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>survival analysis; network analysis; Representation Learning with Blockwise Missingness</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>First-Order Efficiency for Probabilistic Value Estimation via A Statistical Viewpoint (2026)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/andrew.cmu.edu/weijingtang/home</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -571,36 +583,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>agents</t>
+          <t>arborphy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Huimin Cheng</t>
+          <t>Wenpin Hou</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor in Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>huimin23@bu.edu</t>
+          <t>wenpin.hou@duke.edu</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,22 +622,18 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>hallucination in LLMs; network causal inference; graphon cross-validation</t>
+          <t>Trajectory-guided dimensionality reduction; Foundation Model for Single-Cell ATAC-seq; Large Multimodal Models; Biomedical Image Classification; genomic knowledge</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Network perturbation aggregation for graphon estimation (2026)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/view/huimincheng/home/</t>
-        </is>
-      </c>
+          <t>Assessing Large Multimodal Models for One‐Shot Learning and Interpretability in Biomedical Image Classification (2025)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -637,57 +645,57 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>arborphy</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Larry Han</t>
+          <t>Zhicheng Ji</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics and Data Science</t>
+          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>larry_han@brown.edu</t>
+          <t>zhicheng.ji@duke.edu</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>conformal quantile regression; learning causal effects; targeted estimators</t>
+          <t>pretrained model for whole-cell segmentation; LLM-based cell type annotation harmonization; temporal and spatial gene expression patterns; Trajectory-guided dimensionality reduction</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Outcome prediction using image features with conformal quantile regression: application to kidney function (2026)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://larrylehan.github.io/</t>
-        </is>
-      </c>
+          <t>Halo: a pretrained model for whole-cell segmentation from nuclei images in spatial transcriptomics (2026)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -699,46 +707,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PhD Molei Liu</t>
+          <t>Xiao Liu</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Center for Neural Engineering</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ml4890@cumc.columbia.edu</t>
-        </is>
-      </c>
+          <t>Associate Professor of Biomedical Engineering</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>federated learning; semi-supervised learning; transfer learning</t>
+          <t>multimodal neuroimaging techniques; function-related signal features; healthy and diseased brains</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>http://sites.psu.edu/mcnl/</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>B</t>
@@ -758,27 +766,27 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PhD Tian Gu</t>
+          <t>Chuan Hong</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics</t>
+          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>tg2880@cumc.columbia.edu</t>
+          <t>chuan.hong@duke.edu</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -788,15 +796,15 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>generative models for synthetic data generation; fine-tuning large language models; federated learning</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://www.gutian.info/</t>
-        </is>
-      </c>
+          <t>Representation learning to advance multi-institutional studies; Retrieval-augmented generation in medicine; Large language models in global health</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Representation learning to advance multi-institutional studies with electronic health record data from US and France (2026)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>B</t>
@@ -816,45 +824,41 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PhD Wenpin Hou</t>
+          <t>Harikesh S. Wong</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics</t>
+          <t>Assistant Professor of Biology, Core Member, Ragon Institute Education</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>wh2526@cumc.columbia.edu</t>
+          <t>wongs@mit.edu</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>single-cell multiomics; spatial genomics; gene regulatory networks</t>
+          <t>computational modelling; quantitative fluorescence microscopy; intercellular circuits</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://winnie09.github.io/Wenpin_Hou/</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>B</t>
@@ -878,17 +882,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sherry Tongshuang Wu</t>
+          <t>Huimin Cheng</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -898,27 +902,27 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>sherryw@cs.cmu.edu</t>
+          <t>huimin23@bu.edu</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AI evaluation; Discretizing Reward Models; Align AI to Dynamic Human-AI Workflows</t>
+          <t>hallucination in LLMs; network causal inference; graphon cross-validation</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Discretizing Reward Models (2026)</t>
+          <t>Network perturbation aggregation for graphon estimation (2026)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.cs.cmu.edu/~sherryw</t>
+          <t>https://sites.google.com/view/huimincheng/home/</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -940,12 +944,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wei Jin</t>
+          <t>Larry Han</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -955,32 +959,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor of Biostatistics and Data Science</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>weijin@bu.edu</t>
+          <t>larry_han@brown.edu</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bayesian nonparametrics; reinforcement learning; dynamic treatment regimes</t>
+          <t>conformal quantile regression; learning causal effects; targeted estimators</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>The association of PTSD with burden of chronic overlapping pain conditions (2026)</t>
+          <t>Outcome prediction using image features with conformal quantile regression: application to kidney function (2026)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/bluejw</t>
+          <t>https://larrylehan.github.io/</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1002,45 +1006,41 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Xiao Wang</t>
+          <t>Molei Liu</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>xwangx@mit.edu</t>
+          <t>ml4890@cumc.columbia.edu</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>spatially resolved in situ sequencing; multi-modal mapping; computational toolbox</t>
+          <t>federated learning; semi-supervised learning; transfer learning</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://chemistry.mit.edu/profile/xiao-wang/</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>B</t>
@@ -1060,27 +1060,27 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Xin Ma</t>
+          <t>Pixu Shi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics at CUMC</t>
+          <t>Assistant Professor of Biostatistics &amp; Bioinformatics</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>xm2141@cumc.columbia.edu</t>
+          <t>pixu.shi@duke.edu</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1090,22 +1090,18 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>statistical and machine-learning methods for high-dimensional data; medical imaging modalities; functional/object data analysis</t>
+          <t>Panel Flow Matching; Joint Dimensionality Reduction of Longitudinal Multi-omic Data; Trajectory-guided dimensionality reduction; Learning Distributions of Longitudinal Data</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>The aging immune system and all-cause mortality in older americans: differences across sex and race/ethnicity (2025)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://xin-ma-1.github.io</t>
-        </is>
-      </c>
+          <t>Panel Flow Matching: A Generative Approach to Learning Distributions of Longitudinal Data (2026)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1119,19 +1115,15 @@
       <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>arborphy</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ying Ma</t>
+          <t>Tian Gu</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1141,37 +1133,33 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Edens Family Assistant Professor of Healthcare Communications and Technology and Assistant Professor of Biostatistics</t>
+          <t>Assistant Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ying_ma@brown.edu</t>
+          <t>tg2880@cumc.columbia.edu</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>single-cell foundation models; spatial transcriptomics; single-cell RNA-seq</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Accessible and reproducible deployment reveals the practical boundaries of single-cell foundation models (2026)</t>
-        </is>
-      </c>
+          <t>generative models for synthetic data generation; fine-tuning large language models; federated learning</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://yingma0107.github.io</t>
+          <t>https://www.gutian.info/</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1188,27 +1176,27 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zhiliang Bai</t>
+          <t>Wei Jin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Incoming Assistant Professor in the Department of Biological Engineering Intramural member of</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>zlbai@mit.edu</t>
+          <t>weijin@bu.edu</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1218,14 +1206,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AI-driven computational pipelines; integrate multi-omics data with histopathology; spatial multi-omics</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+          <t>Bayesian nonparametrics; reinforcement learning; dynamic treatment regimes</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>The association of PTSD with burden of chronic overlapping pain conditions (2026)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/bluejw</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1242,41 +1238,45 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bin Zhang</t>
+          <t>Wenpin Hou</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Associate Professor of Chemistry Associate Member of the Broad Institute Pfizer</t>
+          <t>Assistant Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>binz@mit.edu</t>
+          <t>wh2526@cumc.columbia.edu</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>novel theoretical and computational approaches; genome organization; dynamical complexity of genome organization</t>
+          <t>single-cell multiomics; spatial genomics; gene regulatory networks</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://winnie09.github.io/Wenpin_Hou/</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>B</t>
@@ -1293,59 +1293,51 @@
       <c r="B15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>agents</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chenyan Xiong</t>
+          <t>Xiao Wang</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>cx@andrew.cmu.edu</t>
+          <t>xwangx@mit.edu</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Generating Pretraining Tokens; Agentic Search; LLM Pretraining</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Beneficial Reasoning Behaviors in Agentic Search and Effective Post-training to Obtain Them (2025)</t>
-        </is>
-      </c>
+          <t>spatially resolved in situ sequencing; multi-modal mapping; computational toolbox</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>http://www.cs.cmu.edu/~cx</t>
+          <t>https://chemistry.mit.edu/profile/xiao-wang/</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1362,7 +1354,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PhD Min Qian</t>
+          <t>Xin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1377,29 +1369,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics</t>
+          <t>Assistant Professor of Biostatistics at CUMC</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>mq2158@cumc.columbia.edu</t>
+          <t>xm2141@cumc.columbia.edu</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>individualized treatment policies; novel statistical methodologies; medical decision making</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+          <t>statistical and machine-learning methods for high-dimensional data; medical imaging modalities; functional/object data analysis</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>The aging immune system and all-cause mortality in older americans: differences across sex and race/ethnicity (2025)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://xin-ma-1.github.io</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1411,22 +1411,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Haolin Li</t>
+          <t>Yandi Shen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>haolinli@bu.edu</t>
+          <t>yandis@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1444,24 +1444,20 @@
           <t>Possible</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>gradient boosting machine for survival prediction; Modified Random Survival Forest; general failure-time outcome-dependent sampling design</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Gradient boosting machine for survival prediction in studies with general failure-time outcome-dependent sampling design (2026)</t>
+          <t>Poisson empirical Bayes estimation: When does g-modeling beat f-modeling in theory (and in practice)? (2026)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/haolin-leo-li-phd</t>
+          <t>https://sayidshen.github.io/</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1473,17 +1469,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>arborphy</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jungwun Lee</t>
+          <t>Ying</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Edens Family Assistant Professor of Healthcare Communications and Technology and Assistant Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>jwlee1@bu.edu</t>
+          <t>ying_ma@brown.edu</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>latent variable modeling; incomplete data analysis; causal inference</t>
+          <t>single-cell foundation models; spatial transcriptomics; single-cell RNA-seq</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A Latent Trajectory Analysis for Multivariate Outcomes with Mixed-Scale: Application to Alzheimer's Disease Neuroimaging Initiative (2026)</t>
+          <t>Accessible and reproducible deployment reveals the practical boundaries of single-cell foundation models (2026)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://sites.google.com/site/leejwegg/</t>
+          <t>https://yingma0107.github.io</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1535,12 +1535,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Linlin Fan</t>
+          <t>Zhiliang Bai</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Professor of Applied Biology, Assistant Professor, The Picower Institute f</t>
+          <t>Incoming Assistant Professor in the Department of Biological Engineering Intramural member of</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>lzfan@mit.edu</t>
+          <t>zlbai@mit.edu</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>neural codes underlying learning and memory; learning rules of brain circuits; identify the physical basis of learning and memory</t>
+          <t>AI-driven computational pipelines; integrate multi-omics data with histopathology; spatial multi-omics</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1589,17 +1589,17 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Youjin Lee</t>
+          <t>Yidan Shi</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1609,14 +1609,10 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics Overview Youjin Lee is a Manning Assistant Prof</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>youjin_lee@brown.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Possible</t>
@@ -1624,22 +1620,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>robust and credible causal inference methods; causal/statistical methods for network and clustered data; difference-in-differences</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Multiply robust difference-in-differences estimation of causal effect curves for continuous exposures (2025)</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>http://www.youjinleeylee.com/</t>
-        </is>
-      </c>
+          <t>causal inference; survival analysis; multi-omics data</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1651,50 +1639,50 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>arborphy</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PhD Yifei Sun</t>
+          <t>Yisong Yue</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>California Institute of Technology</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computation and Neural Systems</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ys3072@cumc.columbia.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor of Computing and Mathematical Sciences</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>statistical and machine learning methods related to time-to-event outcomes; decision tree learning; left truncation bias</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://www.yifei-sun.com</t>
-        </is>
-      </c>
+          <t>foundation model for cell segmentation; time-series health evaluation; Active learning-assisted directed evolution; Reinforcement Learning; LLM Inference Scaling</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>CellSAM: a foundation model for cell segmentation (2025)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>B</t>
@@ -1709,12 +1697,12 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Gene-Wei Li</t>
+          <t>Bin Zhang</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1729,30 +1717,26 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biology Department</t>
+          <t>Associate Professor of Chemistry Associate Member of the Broad Institute Pfizer</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>gwli@mit.edu</t>
+          <t>binz@mit.edu</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>quantitative principles governing gene expression; analytical frameworks; cells work as an optimization process</t>
+          <t>novel theoretical and computational approaches; genome organization; dynamical complexity of genome organization</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://biology.mit.edu/people/gene_wei_li</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>B</t>
@@ -1767,12 +1751,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ScD Zhonghua Liu</t>
+          <t>Min Qian</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1787,16 +1771,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Associate Professor of Biostatistics</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>mq2158@cumc.columbia.edu</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>individualized treatment policies; novel statistical methodologies; medical decision making</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -1813,34 +1805,30 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PhD Qixuan Chen</t>
+          <t>Dezhe Jin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Center for Neural Engineering</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>qc2138@cumc.columbia.edu</t>
-        </is>
-      </c>
+          <t>Associate Professor of Physics</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -1848,11 +1836,15 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>analyzing complex surveys; survey sampling; handling data with missing values or measurement errors</t>
+          <t>theoretical analysis of biological neural networks; computational models of song generation; learning and memory in the hippocampus</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>http://personal.psu.edu/dzj2/ShuTu/</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>B</t>
@@ -1863,7 +1855,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>east_asian</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1872,37 +1864,33 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Yunha Hwang</t>
+          <t>Jiyuan Hu</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>yunha@mit.edu</t>
-        </is>
-      </c>
+          <t>Associate Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>developing machine learning models; discover and design novel microbial functions; microbial evolution, ecology and biochemistry</t>
+          <t>analysis of high-dimensional; EHR data; multi-modal data</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1917,7 +1905,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>east_asian</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1926,29 +1914,25 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Seung Hoan Choi</t>
+          <t>Xiaogang Hu</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Center for Neural Engineering</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Research Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>seuchoi@bu.edu</t>
-        </is>
-      </c>
+          <t>Dorothy Foehr Huck and J. Lloyd Huck Chair in Neurorehabilitation Associate Professor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -1956,22 +1940,18 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>statistical genetics methods; whole-genome and whole-exome sequencing; rare and common variant analyses</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Multiple-testing corrections in case-control studies using identity-by-descent segments (2026)</t>
-        </is>
-      </c>
+          <t>neural-machine interface techniques; neuromechanics of the arm and hand; after neural or muscular injuries</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://sites-staging.bu.edu/shclab/</t>
+          <t>https://sites.psu.edu/nml1/</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -1979,617 +1959,577 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>south_asian</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>agents</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aditi Raghunathan</t>
+          <t>Chan Wang</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>raditi@cmu.edu</t>
-        </is>
-      </c>
+          <t>Research Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>distribution shift; agent safety; quantization pipelines</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Scalable Weak-to-Strong Verifier Hardening for Agent Environments (2026)</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>https://www.cs.cmu.edu/~aditirag</t>
-        </is>
-      </c>
+          <t>statistical methodologies for high-throughput data; sequencing data; integrating these omics datasets</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
       <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jenelle Feather</t>
+          <t>Ting-Fang Lee</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Assistant Professor, Neuroscience Institute, Psychology</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>jfeather@cmu.edu</t>
-        </is>
-      </c>
+          <t>Research Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>adversarial robustness; DNN prediction accuracy; model-optimized stimulus distortions</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Neural prediction decorrelation reveals that adversarial robustness substantially improves DNN prediction accuracy across the entire human auditory cortex (2026)</t>
-        </is>
-      </c>
+          <t>intricate data structures; network-based studies; advanced mathematical tools to machine learning algorithms</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Haolin Li</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Boston University</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>haolinli@bu.edu</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>gradient boosting machine for survival prediction; Modified Random Survival Forest; general failure-time outcome-dependent sampling design</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Gradient boosting machine for survival prediction in studies with general failure-time outcome-dependent sampling design (2026)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/haolin-leo-li-phd</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>agents</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Daniel Fried</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Carnegie Mellon University</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Language Technologies Institute</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jungwun Lee</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Boston University</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Assistant Professor</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>dfried@andrew.cmu.edu</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>jwlee1@bu.edu</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>LLM agents; code generation; Tree Search for Language Model Agents</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Tree Search for Language Model Agents (2024)</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>https://dpfried.github.io</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>latent variable modeling; incomplete data analysis; causal inference</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>A Latent Trajectory Analysis for Multivariate Outcomes with Mixed-Scale: Application to Alzheimer's Disease Neuroimaging Initiative (2026)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/site/leejwegg/</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Lukas M Weber</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Boston University</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Linlin Fan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Computational and Systems Biology</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Professor of Applied Biology, Assistant Professor, The Picower Institute f</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>lzfan@mit.edu</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>neural codes underlying learning and memory; learning rules of brain circuits; identify the physical basis of learning and memory</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Youjin Lee</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Brown University</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Biostatistics</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>lmweber@bu.edu</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Biostatistics Overview Youjin Lee is a Manning Assistant Prof</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>youjin_lee@brown.edu</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>statistical genomics; spatial transcriptomics; Spatially orthogonal factor models</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Spatially orthogonal factor models for spatial transcriptomics and remote sensing data (2026)</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://lmweber.org/</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>robust and credible causal inference methods; causal/statistical methods for network and clustered data; difference-in-differences</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Multiply robust difference-in-differences estimation of causal effect curves for continuous exposures (2025)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>http://www.youjinleeylee.com/</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Saurabh Vyas</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Carnegie Mellon University</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Neuroscience Institute</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Assistant Professor, Neuroscience Institute and Biomedical Engineering</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>vyas@cmu.edu</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Yifei Sun</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Columbia University</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Associate Professor of Biostatistics</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ys3072@cumc.columbia.edu</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>statistical and machine learning methods related to time-to-event outcomes; decision tree learning; left truncation bias</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://www.yifei-sun.com</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Zhiguo Li</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Duke University</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Biostatistics &amp; Bioinformatics</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Associate Professor of Biostatistics &amp; Bioinformatics</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Win Ratio as an Effect Size Measure; Weighted Logrank Test; interval censored survival data; sequential multiple assignment randomized trials</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Analysis of interval censored survival data in sequential multiple assignment randomized trials (2025)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Gene-Wei Li</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Computational and Systems Biology</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Biology Department</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>gwli@mit.edu</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>neural population dynamics; large-scale neural population electrophysiology; brain-computer interfaces</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Understanding Strategic Motor Learning as a Process of Hypothesis Testing (2026)</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://grassfoundation.org/people/saurabh-vyas/</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Steven Flavell</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Massachusetts Institute of Technology</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Computational and Systems Biology</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>flavell@mit.edu</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>in vivo calcium imaging; quantitative behavioral analyses; neuromodulators like serotonin</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>https://bcs.mit.edu/users/flavell</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Ani Eloyan</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Brown University</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Biostatistics</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Vice Chair of the Department of Biostatistics,   Associate Professor of Biostatistics</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ani_eloyan@brown.edu</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>semi-parametric likelihood based methods for matrix decompositions; statistical analyses of brain images; integration of various types of complex data structures</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Computational learning phenotypes are not related to individual differences in resting-state fMRI connectivity (2026)</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Ila Fiete</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Massachusetts Institute of Technology</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Computational and Systems Biology</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Associate Professor</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>fiete@mit.edu</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>architecture and dynamics of neural circuits; coding states evolve to perform computations; learning, memory, integration, inference</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>https://bcs.mit.edu/users/fietemitedu</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Anda Chirila</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Brown University</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Neuroscience</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Manning Assistant Professor of Neuroscience</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>anda_chirila@brown.edu</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Possible</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>calcium imaging; large-scale spinal cord electrophysiology; computational approaches</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Targeting Gi/o-coupled GPCRs to inhibit nociceptors: Insights from the serotonin receptor Htr1b and triptans (2026)</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>quantitative principles governing gene expression; analytical frameworks; cells work as an optimization process</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://biology.mit.edu/people/gene_wei_li</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Andreas Pfenning</t>
+          <t>Yuyan Wang</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Assistant Professor, Computational Biology and Neuroscience Institute</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>apfenning@cmu.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>computational and genomic tools; single-cell RNA-seq; comparative genomics</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Conditional polygenic enrichment distinguishes causal from tagging disease-critical cell populations in single-cell RNA-seq (2026)</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>http://www.pfenninglab.org/</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Arman Oganisian</t>
+          <t>Qixuan Chen</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2599,104 +2539,112 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thomas J. &amp; Alice M. Tisch Assistant Professor of Biostatistics</t>
+          <t>Associate Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>arman_oganisian@brown.edu</t>
+          <t>qc2138@cumc.columbia.edu</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Bayesian semiparametric methods; Bayesian nonparametric methods for causal estimation; sequential treatment strategies</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Untangling sample and population level estimands in Bayesian causal computation (2026)</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://stablemarkets.netlify.app/</t>
-        </is>
-      </c>
+          <t>analyzing complex surveys; survey sampling; handling data with missing values or measurement errors</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>east_asian</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>flywire</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>David Choi</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Department of Statistics &amp; Data Science</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Associate Professor of Statistics and Information Systems</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>davidch@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>machine learning for network data; community detection; causal inference</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Balancing weights for region-level analysis: The effect of Medicaid expansion on the uninsurance rate among states that did not expand Medicaid (2023)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>http://www.andrew.cmu.edu/user/davidch/</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Caroline Uhler</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Massachusetts Institute of Technology</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Computational and Systems Biology</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>cuhler@mit.edu</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>probabilistic graphical models; algebraic structure in graphical models; statistical and computational limitations for learning</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://www.eecs.mit.edu/people/faculty/caroline-uhler</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>east_asian</t>
+        </is>
+      </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Connor W. Coley</t>
+          <t>Yunha Hwang</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2711,12 +2659,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Assistant Professor in Chemical Engineering Department</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ccoley@mit.edu</t>
+          <t>yunha@mit.edu</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2726,15 +2674,11 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>computer-assistance for chemical discovery; laboratory automation; platform technologies</t>
+          <t>developing machine learning models; discover and design novel microbial functions; microbial evolution, ecology and biochemistry</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://cheme.mit.edu/profile/connor-w-coley/</t>
-        </is>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>B</t>
@@ -2743,114 +2687,98 @@
       <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>east_asian</t>
+        </is>
+      </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>interp</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Daphne Ippolito</t>
+          <t>Cheongeun Oh</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>daphnei@cmu.edu</t>
-        </is>
-      </c>
+          <t>Associate Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>language generation systems; show its workings; Measuring Weak-to-Strong Legibility</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>AI can learn to show its workings through trial and error (2025)</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://www.daphnei.com</t>
-        </is>
-      </c>
+          <t>Bayesian modeling; causal inference; clinical trial design</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>east_asian</t>
+        </is>
+      </c>
       <c r="B41" t="n">
         <v>3</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>David Sontag</t>
+          <t>Yongsoo Kim</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Center for Neural Engineering</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Assistant Professor of Electrical Engineering and Computer Science</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>dsontag@mit.edu</t>
-        </is>
-      </c>
+          <t>Associate Professor of Neural and Behavioral Sciences</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>research interests are in machine learning and artificial intelligence; transform healthcare through the use of machine learning; Computer Science and Artificial Intelligence Laboratory</t>
+          <t>Mapping Brain Cellular Architecture; 3D mapping techniques; autism spectrum disorders</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://www.eecs.mit.edu/people/faculty/david-sontag</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>B</t>
@@ -2859,179 +2787,155 @@
       <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>east_asian</t>
+        </is>
+      </c>
       <c r="B42" t="n">
         <v>3</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Eric Yttri</t>
+          <t>Seung Hoan Choi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Assistant Professor, Biological Sciences and Neuroscience Institute</t>
+          <t>Research Assistant Professor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>eyttri@andrew.cmu.edu</t>
+          <t>seuchoi@bu.edu</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>cross-population amplitude coupling; high-dimensional oscillatory neural time series; keypoint-less behavior platform</t>
+          <t>statistical genetics methods; whole-genome and whole-exome sequencing; rare and common variant analyses</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>B-REAL: A keypoint-less behavior platform for offline classification and real-time detection (2026)</t>
+          <t>Multiple-testing corrections in case-control studies using identity-by-descent segments (2026)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://labs.bio.cmu.edu/yttri/</t>
+          <t>https://sites-staging.bu.edu/shclab/</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>east_asian</t>
+        </is>
+      </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Gonzalo Mena</t>
+          <t>Hyungrok Do</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Assistant Professor, Department of Statistics and Data Science</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>gmena@andrew.cmu.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>optimal transport; causal inference; heterogeneity in cognitive decline</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Statistical Rates for Entropic Optimal Transport in the Discrete to SubGaussian Regime (2026)</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>http://gomena.github.io/</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>south_asian</t>
+        </is>
+      </c>
       <c r="B44" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>calcium</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Leenoy Meshulam</t>
+          <t>Jayeeta Basu</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neuroscience</t>
+          <t>Center for Neural Science</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Assistant Professor of Neuroscience,   Assistant Professor of Physics,   Robert J. and Nancy D. Carney Assistant Professor of Brain Science</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>leenoy_meshulam@brown.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor of Physiology and Neuroscience (School of Medicine), and Neural Science;</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>statistical-physics approaches; large networks of cells; collective function</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Hierarchical processing and polarization encoding in the cephalopod visual system (2026)</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3039,16 +2943,16 @@
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>agents</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Maarten Sap</t>
+          <t>Jenelle Feather</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3058,17 +2962,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Neuroscience Institute</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor, Neuroscience Institute, Psychology</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>msap2@andrew.cmu.edu</t>
+          <t>jfeather@cmu.edu</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3078,22 +2982,18 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>social intelligence; theory of mind; pragmatic understanding</t>
+          <t>adversarial robustness; DNN prediction accuracy; model-optimized stimulus distortions</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>XYBench: Can LLMs Respond Pragmatically to Queries with Misconceptions? (2026)</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>https://maartensap.com</t>
-        </is>
-      </c>
+          <t>Neural prediction decorrelation reveals that adversarial robustness substantially improves DNN prediction accuracy across the entire human auditory cortex (2026)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3101,22 +3001,26 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Matthew G. Jones</t>
+          <t>Lukas M Weber</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3126,7 +3030,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>mgjones@mit.edu</t>
+          <t>lmweber@bu.edu</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3136,14 +3040,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>developing new computational methods to trace cellular lineages; integrate advances in computation and AI; copy-number alterations</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+          <t>statistical genomics; spatial transcriptomics; Spatially orthogonal factor models</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Spatially orthogonal factor models for spatial transcriptomics and remote sensing data (2026)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://lmweber.org/</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3151,32 +3063,36 @@
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Olivia Corradin</t>
+          <t>Saurabh Vyas</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Neuroscience Institute</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biology Education</t>
+          <t>Assistant Professor, Neuroscience Institute and Biomedical Engineering</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>corradin@wi.mit.edu</t>
+          <t>vyas@cmu.edu</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3186,18 +3102,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>genetic and epigenetic variation; disease-associated variants; gene regulation</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>neural population dynamics; large-scale neural population electrophysiology; brain-computer interfaces</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Understanding Strategic Motor Learning as a Process of Hypothesis Testing (2026)</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://csbphd.mit.edu/faculty_spotlight/olivia-corradin/</t>
+          <t>https://grassfoundation.org/people/saurabh-vyas/</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3205,32 +3125,36 @@
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PhD Caleb Miles</t>
+          <t>Steven Flavell</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Assistant Professor, Biostatistics</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>cm3825@cumc.columbia.edu</t>
+          <t>flavell@mit.edu</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3240,13 +3164,13 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>semiparametric methods for causal inference; intersection with machine learning; mediation analysis</t>
+          <t>in vivo calcium imaging; quantitative behavioral analyses; neuromodulators like serotonin</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://calebhmiles.github.io</t>
+          <t>https://bcs.mit.edu/users/flavell</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3259,57 +3183,57 @@
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Prasad Patil</t>
+          <t>Aaditya Rangan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Center for Neural Science</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor of Mathematics and Neural Science;</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>patil@bu.edu</t>
+          <t>rangan@cims.nyu.edu</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Stable and interpretable prediction methods; gene expression data; Reducing overconfident errors</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Reducing overconfident errors in clinical prediction models (2026)</t>
-        </is>
-      </c>
+          <t>computational and statistical tools; high-dimensional problems; computational genomics; computational neuroscience</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>http://prasadpatil.net/</t>
+          <t>http://www.cims.nyu.edu/~rangan/CV_20261019</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3317,58 +3241,54 @@
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>agents</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sean Welleck</t>
+          <t>Ani Eloyan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Vice Chair of the Department of Biostatistics,   Associate Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>swelleck@andrew.cmu.edu</t>
+          <t>ani_eloyan@brown.edu</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>inference algorithms for language models; formal theorem proving; Benchmarking AI agents</t>
+          <t>semi-parametric likelihood based methods for matrix decompositions; statistical analyses of brain images; integration of various types of complex data structures</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Into the Unknown: Benchmarking AI agents on open scientific research problems (2026)</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>https://wellecks.com</t>
-        </is>
-      </c>
+          <t>Computational learning phenotypes are not related to individual differences in resting-state fMRI connectivity (2026)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>A</t>
@@ -3379,7 +3299,7 @@
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -3388,52 +3308,48 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Shariq Mohammed</t>
+          <t>Ila Fiete</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>shariqm@bu.edu</t>
+          <t>fiete@mit.edu</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Bayesian modeling; Bayesian Feature Extraction; spatial statistics</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Bayesian Feature Extraction using Gaussian and Diffused-gamma Priors for High Dimensional Spatio-Temporal Data (2026)</t>
-        </is>
-      </c>
+          <t>architecture and dynamics of neural circuits; coding states evolve to perform computations; learning, memory, integration, inference</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://shariq-mohammed.github.io/</t>
+          <t>https://bcs.mit.edu/users/fietemitedu</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3443,28 +3359,36 @@
       <c r="B52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PhD Daniel Malinsky</t>
+          <t>Anda Chirila</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Manning Assistant Professor of Neuroscience</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>anda_chirila@brown.edu</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>Possible</t>
@@ -3472,18 +3396,18 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>graphical structure learning; causal discovery; semiparametric inference</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>https://www.dmalinsky.com</t>
-        </is>
-      </c>
+          <t>calcium imaging; large-scale spinal cord electrophysiology; computational approaches</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Targeting Gi/o-coupled GPCRs to inhibit nociceptors: Insights from the serotonin receptor Htr1b and triptans (2026)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3496,25 +3420,29 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Rafael Gomez-Bombarelli</t>
+          <t>Andreas Pfenning</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Neuroscience Institute</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Assistant Professor in Materials Processing, Jeffrey Cheah Career Development Profes</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Assistant Professor, Computational Biology and Neuroscience Institute</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>apfenning@cmu.edu</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>Possible</t>
@@ -3522,18 +3450,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>fuse machine learning and atomistic simulations; embedding domain expertise and experimental results into their models; scaled to practical applications</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>computational and genomic tools; single-cell RNA-seq; comparative genomics</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Conditional polygenic enrichment distinguishes causal from tagging disease-critical cell populations in single-cell RNA-seq (2026)</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://csbphd.mit.edu/faculty_spotlight/rafael-gomez-bombarelli/</t>
+          <t>http://www.pfenninglab.org/</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -3546,48 +3478,52 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Adam Martin</t>
+          <t>Ankit Pensia</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Associate Professor of Biology Department</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>acmartin@mit.edu</t>
+          <t>ankitp@cmu.edu</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>imaging integrated with computational analysis; tissue shape emerges; collective cellular behaviors</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>robust and heavy-tailed statistics; inference under constraints; Fast Algorithms for Sparse PCA and Robust Sparse Estimation</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Fast Algorithms for Sparse PCA and Robust Sparse Estimation (2026)</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://biology.mit.edu/people/adam_martin</t>
+          <t>https://ankitp.net/</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -3600,7 +3536,7 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Jon Steingrimsson</t>
+          <t>Arman Oganisian</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3615,30 +3551,34 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics, Director of the NextGen Graduate Program in Biostatistics</t>
+          <t>Thomas J. &amp; Alice M. Tisch Assistant Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>jon_steingrimsson@brown.edu</t>
+          <t>arman_oganisian@brown.edu</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>generalizing or transporting treatment effects; machine learning algorithms for risk prediction with censored data; treatment effect heterogeneity</t>
+          <t>Bayesian semiparametric methods; Bayesian nonparametric methods for causal estimation; sequential treatment strategies</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Estimating and Evaluating Counterfactual Prediction Models (2025)</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+          <t>Untangling sample and population level estimands in Bayesian causal computation (2026)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://stablemarkets.netlify.app/</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>A</t>
@@ -3654,43 +3594,43 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Laurie A. Boyer</t>
+          <t>Caleb Miles</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Associate Professor Of Biology and Biological Engineering Department</t>
+          <t>Assistant Professor, Biostatistics</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>lboyer@mit.edu</t>
+          <t>cm3825@cumc.columbia.edu</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>integrative computational and experimental approaches; epigenomic map; transcriptional and chromatin regulatory mechanisms</t>
+          <t>semiparametric methods for causal inference; intersection with machine learning; mediation analysis</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://csbphd.mit.edu/faculty_spotlight/boyer/</t>
+          <t>https://calebhmiles.github.io</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3708,43 +3648,43 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PhD Jeff Goldsmith</t>
+          <t>Caroline Uhler</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>jeff.goldsmith@columbia.edu</t>
+          <t>cuhler@mit.edu</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>functional data analysis; physical activity monitoring; skilled movements</t>
+          <t>probabilistic graphical models; algebraic structure in graphical models; statistical and computational limitations for learning</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://jeffgoldsmith.com/</t>
+          <t>https://www.eecs.mit.edu/people/faculty/caroline-uhler</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3762,7 +3702,7 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tamara Broderick</t>
+          <t>Connor W. Coley</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3777,28 +3717,28 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor in Chemical Engineering Department</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>tbroderick@csail.mit.edu</t>
+          <t>ccoley@mit.edu</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Bayesian inference; graphical models; unsupervised learning</t>
+          <t>computer-assistance for chemical discovery; laboratory automation; platform technologies</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://csbphd.mit.edu/faculty_spotlight/broderick/</t>
+          <t>https://cheme.mit.edu/profile/connor-w-coley/</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3811,12 +3751,12 @@
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Alex K. Shalek</t>
+          <t>David Sontag</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3831,12 +3771,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Assistant Professor of Electrical Engineering and Computer Science</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>shalek@mit.edu</t>
+          <t>dsontag@mit.edu</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3846,13 +3786,13 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>creation and implementation of new technologies; systems-level functions; ensemble cellular behaviors</t>
+          <t>research interests are in machine learning and artificial intelligence; transform healthcare through the use of machine learning; Computer Science and Artificial Intelligence Laboratory</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>http://imes.mit.edu/people/faculty/shalek-alex-k/</t>
+          <t>https://www.eecs.mit.edu/people/faculty/david-sontag</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3865,32 +3805,36 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Alyssa Bilinski</t>
+          <t>Eric Yttri</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Neuroscience Institute</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Peterson Family Assistant Professor of Health Policy, Assistant Professor of Health Services, Policy and Practice and Biostatistics</t>
+          <t>Assistant Professor, Biological Sciences and Neuroscience Institute</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>alyssa_bilinski@brown.edu</t>
+          <t>eyttri@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3900,22 +3844,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Difference-in-Differences; Parallel Trends; developing novel methods to support decision-making</t>
+          <t>cross-population amplitude coupling; high-dimensional oscillatory neural time series; keypoint-less behavior platform</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Nothing to See Here? A Non‐Inferiority Approach to Parallel Trends (2026)</t>
+          <t>B-REAL: A keypoint-less behavior platform for offline classification and real-time detection (2026)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://www.alyssabilinski.com</t>
+          <t>https://labs.bio.cmu.edu/yttri/</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -3923,32 +3867,32 @@
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Anders Sejr Hansen</t>
+          <t>Gonzalo Mena</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Neuroscience Institute</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biological Engineering Department</t>
+          <t>Assistant Professor, Department of Statistics and Data Science</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ashansen@mit.edu</t>
+          <t>gmena@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3958,18 +3902,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>super resolution microscopy; 3D genome architecture; chromatin looping</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>optimal transport; causal inference; heterogeneity in cognitive decline</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Statistical Rates for Entropic Optimal Transport in the Discrete to SubGaussian Regime (2026)</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://be.mit.edu/directory/anders-sejr-hansen</t>
+          <t>http://gomena.github.io/</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -3977,32 +3925,36 @@
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Drew Beauchamp</t>
+          <t>Leenoy Meshulam</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Assistant Professor, Neuroscience Institute, Biomedical Engineering</t>
+          <t>Assistant Professor of Neuroscience,   Assistant Professor of Physics,   Robert J. and Nancy D. Carney Assistant Professor of Brain Science</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>jabeauchamp@cmu.edu</t>
+          <t>leenoy_meshulam@brown.edu</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4012,19 +3964,15 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>motor unit discharge; human-machine interfaces; motoneuron discharge</t>
+          <t>statistical-physics approaches; large networks of cells; collective function</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Reverse engineering of motor unit discharge in multiple sclerosis reveals heterogeneity of voluntary motor commands (2026)</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>https://beauchamplab.org/</t>
-        </is>
-      </c>
+          <t>Hierarchical processing and polarization encoding in the cephalopod visual system (2026)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>A</t>
@@ -4035,22 +3983,22 @@
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fatema Shafie Khorassani</t>
+          <t>Matthew G. Jones</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4060,7 +4008,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>fshafie@bu.edu</t>
+          <t>mgjones@mit.edu</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4070,22 +4018,14 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>statistical methods for surrogate endpoints; causal inference for observational data; survival analysis</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Continuous associations of the brief Wisconsin inventory of smoking dependence motives with transitions between cigarette and e-cigarette use (2026)</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>https://www.fatemashafie.com/</t>
-        </is>
-      </c>
+          <t>developing new computational methods to trace cellular lineages; integrate advances in computation and AI; copy-number alterations</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -4093,32 +4033,32 @@
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Jonathan Tsay</t>
+          <t>Olivia Corradin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Assistant Professor, Neuroscience Institute</t>
+          <t>Assistant Professor of Biology Education</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>jstsay@cmu.edu</t>
+          <t>corradin@wi.mit.edu</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4128,15 +4068,15 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Large reaching datasets; Strategic Motor Learning; hidden dynamics of proprioception</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Tracking the hidden dynamics of proprioception (2026)</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
+          <t>genetic and epigenetic variation; disease-associated variants; gene regulation</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://csbphd.mit.edu/faculty_spotlight/olivia-corradin/</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>B</t>
@@ -4147,17 +4087,17 @@
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Stavroula Chrysanthopoulou</t>
+          <t>Prasad Patil</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4167,12 +4107,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics, Director of the Master's Graduate Program in Biostatistics</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stavroula_chrysanthopoulou@brown.edu</t>
+          <t>patil@bu.edu</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4182,15 +4122,19 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>microsimulation modeling; complex predictive models applied in medical decision making; natural history of lung cancer</t>
+          <t>Stable and interpretable prediction methods; gene expression data; Reducing overconfident errors</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Modeling Recurrent Events: A Tutorial Based on Relapse and Remitting Episodes during Medication-Assisted Treatment for Opioid Use Disorder (2025)</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>Reducing overconfident errors in clinical prediction models (2026)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>http://prasadpatil.net/</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>A</t>
@@ -4201,17 +4145,21 @@
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>2</v>
-      </c>
-      <c r="C66" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>calcium</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Alice Paul</t>
+          <t>Shariq Mohammed</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4221,32 +4169,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics Overview I am an Assosciate Professor of Biosta</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>alice_paul@brown.edu</t>
+          <t>shariqm@bu.edu</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>optimization algorithms underlying machine learning; variable selection; shared mobility systems</t>
+          <t>Bayesian modeling; Bayesian Feature Extraction; spatial statistics</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Estimating Censored Spatial-Temporal Demand with Applications to Shared Micromobility (2023)</t>
+          <t>Bayesian Feature Extraction using Gaussian and Diffused-gamma Priors for High Dimensional Spatio-Temporal Data (2026)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>http://alicepaul.github.io</t>
+          <t>https://shariq-mohammed.github.io/</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4259,12 +4207,12 @@
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Emma Strubell</t>
+          <t>Will Townes</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4274,42 +4222,38 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>estrubel@andrew.cmu.edu</t>
+          <t>ftownes@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Not recruiting</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>efficient and equitable natural language processing; Energy Use; Model Life Cycle Assessment</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>The Hidden Cost of Thinking: Energy Use and Environmental Impact of LMs Beyond Pretraining (2026)</t>
-        </is>
-      </c>
+          <t>single cell RNA-Seq; spatial transcriptomics; dimension reduction</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://strubell.github.io</t>
+          <t>https://willtownes.github.io</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -4317,48 +4261,44 @@
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paul C. Blainey</t>
+          <t>Daniel Malinsky</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Associate Professor of Biological Engineering Core Member, Broad Institute of Harvar</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>pblainey@broadinstitute.org</t>
-        </is>
-      </c>
+          <t>Assistant Professor of Biostatistics</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>cutting-edge microfluidic, molecular, and optical methods; reliable, high-quality data; throughput of biological experimentation</t>
+          <t>graphical structure learning; causal discovery; semiparametric inference</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://be.mit.edu/directory/paul-blainey</t>
+          <t>https://www.dmalinsky.com</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4371,53 +4311,49 @@
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PhD Christine Mauro</t>
+          <t>Dean Mobbs</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>California Institute of Technology</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computation and Neural Systems</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics at CUMC</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>cmm2212@cumc.columbia.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor of Cognitive Neuroscience</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>statistical learning techniques; longitudinal data analysis; analysis of clinical trials</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>https://christinemauro.com/</t>
-        </is>
-      </c>
+          <t>Psychometric Evaluation of LLMs; Generative Models of Attitude Change; flexible model-based inference; entorhinal-hippocampal circuit</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Rethinking Psychometric Evaluation of LLMs: When and Why Self-Reports Predict Behavior (2026)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -4425,17 +4361,17 @@
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PhD Linda Valeri</t>
+          <t>Gary Hettinger</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4445,22 +4381,18 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>lv2424@cumc.columbia.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor, Departments of Population Health and Medicine</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>multistate approach; interventions on an intermediate time-to-event; health disparities research</t>
+          <t>statistical methods for causal inference; quasi-experimental designs; comparative effectiveness</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4475,48 +4407,44 @@
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tami Lieberman</t>
+          <t>Justin Silverman</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Center for Neural Engineering</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Associate Professor of Institute for Medical Engineering and Science &amp; Civil and Env</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>tami@mit.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor of Information Science &amp; Technology, Statistics, and Medicine</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>human microbiome; selective pressures they face; niche ranges</t>
+          <t>genomics and electronic health data; analysis of biomedical data; theoretical and applied aspects of mathematics and statistics</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://imes.mit.edu/people/faculty/tami-lieberman/</t>
+          <t>https://jsilve24.github.io/SilvermanLab/</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4529,57 +4457,45 @@
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Yonatan Bisk</t>
+          <t>Nicholas Illenberger</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Language Technologies Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>ybisk@cs.cmu.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>embodied AI; language-conditioned robot manipulation; Multimodal Machine Learning</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Bridging language and action: A survey of language-conditioned robot manipulation (2026)</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>https://yonatanbisk.com</t>
-        </is>
-      </c>
+          <t>causal inference; semiparametric estimation; treatment effect heterogeneity</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -4587,42 +4503,46 @@
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PhD Hanga Galfalvy</t>
+          <t>Rafael Gomez-Bombarelli</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics (in Psychiatry) at CUMC</t>
+          <t>Assistant Professor in Materials Processing, Jeffrey Cheah Career Development Profes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>prediction models for suicide; statistical genetics; analysis of multidimensional longitudinally measured data</t>
+          <t>fuse machine learning and atomistic simulations; embedding domain expertise and experimental results into their models; scaled to practical applications</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://csbphd.mit.edu/faculty_spotlight/rafael-gomez-bombarelli/</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>B</t>
@@ -4633,32 +4553,32 @@
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Vibha Viswanathan</t>
+          <t>Adam Martin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Research Scientist (Special Faculty), Neuroscience Institute</t>
+          <t>Associate Professor of Biology Department</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>vibhavis@andrew.cmu.edu</t>
+          <t>acmartin@mit.edu</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4668,15 +4588,15 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Auditory Scene Analysis; Induced alpha and beta electroencephalographic rhythms; single-trial speech intelligibility</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Prediction from Statistical Learning Aids Auditory Scene Analysis (2026)</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+          <t>imaging integrated with computational analysis; tissue shape emerges; collective cellular behaviors</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://biology.mit.edu/people/adam_martin</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>B</t>
@@ -4687,54 +4607,50 @@
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Anarina Murillo</t>
+          <t>Cosma Shalizi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>anarina_murillo@brown.edu</t>
+          <t>cshalizi@stat.cmu.edu</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>statistics education; measurement error; longitudinal data</t>
+          <t>statistical inference for complex systems; nonparametric prediction for stochastic processes; causal inference; networks and information flow in neuroscience</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>A comparison of methods for coding race in linear and logistic regression models (2025)</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>https://www.anarinalm.com/</t>
-        </is>
-      </c>
+          <t>Bootstrapping Generalization Error Bounds for Time Series (2026)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>A</t>
@@ -4745,48 +4661,48 @@
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bryan Bryson</t>
+          <t>Jeff Goldsmith</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biological Engineering Department</t>
+          <t>Associate Professor of Biostatistics</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>bryand@mit.edu</t>
+          <t>jeff.goldsmith@columbia.edu</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>dynamics of bacterial infection; quantitative modeling; reverse-engineering a vaccine for tuberculosis</t>
+          <t>functional data analysis; physical activity monitoring; skilled movements</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://csbphd.mit.edu/faculty_spotlight/bryson/</t>
+          <t>https://jeffgoldsmith.com/</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -4799,53 +4715,53 @@
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Francisco J. Sánchez-Rivera</t>
+          <t>Jon Steingrimsson</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biology</t>
+          <t>Associate Professor of Biostatistics, Director of the NextGen Graduate Program in Biostatistics</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>fsr@mit.edu</t>
+          <t>jon_steingrimsson@brown.edu</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>genetic variation shapes normal physiology and disease; with a focus on cancer; normal physiology</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>https://biology.mit.edu/profile/francisco-j-sanchez-rivera/</t>
-        </is>
-      </c>
+          <t>generalizing or transporting treatment effects; machine learning algorithms for risk prediction with censored data; treatment effect heterogeneity</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Estimating and Evaluating Counterfactual Prediction Models (2025)</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -4853,12 +4769,12 @@
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Joseph H. Davis</t>
+          <t>Laurie A. Boyer</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4873,24 +4789,28 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biology Department</t>
+          <t>Associate Professor Of Biology and Biological Engineering Department</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>jhdavis@mit.edu</t>
+          <t>lboyer@mit.edu</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>integrative computational and experimental approaches; epigenomic map; transcriptional and chromatin regulatory mechanisms</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://biology.mit.edu/people/jhdavis</t>
+          <t>https://csbphd.mit.edu/faculty_spotlight/boyer/</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -4903,49 +4823,57 @@
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kevin M. Esvelt</t>
+          <t>Nynke Niezink</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Assistant Professor of Media Arts and Science NEC Career Development Professor of Co</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>esvelt@mit.edu</t>
+          <t>nynke@stat.cmu.edu</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>statistical inference for social network data; relational event models; multiplex networks</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Social Relations and Academic Performance: A Network Perspective on Sense of Belonging (2026)</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>http://www.sculptingevolution.org/</t>
+          <t>http://www.stat.cmu.edu/~nynke/</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -4953,12 +4881,12 @@
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lindsay Case</t>
+          <t>Tamara Broderick</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4973,24 +4901,28 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biology Department</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>lcase@mit.edu</t>
+          <t>tbroderick@csail.mit.edu</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Bayesian inference; graphical models; unsupervised learning</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://biology.mit.edu/profile/lindsay-case/</t>
+          <t>https://csbphd.mit.edu/faculty_spotlight/broderick/</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5003,17 +4935,17 @@
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PhD Xiaoyu Che</t>
+          <t>Iván Díaz</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5023,26 +4955,22 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics (In the Center for Infection and Immunity) at CUMC</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>xc2273@cumc.columbia.edu</t>
-        </is>
-      </c>
+          <t>Associate Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Possible</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>statistical methods for causal inference; mediation analysis; covariate adjustment in randomized trials</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>https://www.publichealth.columbia.edu/research/faculty-research-labs-programs</t>
-        </is>
-      </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>B</t>
@@ -5053,32 +4981,32 @@
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sossena Wood</t>
+          <t>Alex K. Shalek</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Assistant Professor, Biomedical Engineering and Neuroscience Institute</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>scwood@andrew.cmu.edu</t>
+          <t>shalek@mit.edu</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5088,17 +5016,13 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Computational Fluid Dynamics; Patient-Specific Modeling; Central Sensitization</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Computational Fluid Dynamics Analysis of Cerebrovascular Hemodynamic Differences in Adults with Sickle Cell Disease: Comparing Stroke and Non-Stroke Cohorts (2026)</t>
-        </is>
-      </c>
+          <t>creation and implementation of new technologies; systems-level functions; ensemble cellular behaviors</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://www.sossenawood.com/</t>
+          <t>http://imes.mit.edu/people/faculty/shalek-alex-k/</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -5111,12 +5035,12 @@
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Claudio Battiloro</t>
+          <t>Alyssa Bilinski</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5131,21 +5055,37 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Assistant Professor of Biostatistics and Data Science</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Peterson Family Assistant Professor of Health Policy, Assistant Professor of Health Services, Policy and Practice and Biostatistics</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>alyssa_bilinski@brown.edu</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>Possible</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Difference-in-Differences; Parallel Trends; developing novel methods to support decision-making</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Nothing to See Here? A Non‐Inferiority Approach to Parallel Trends (2026)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://www.alyssabilinski.com</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -5153,53 +5093,53 @@
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Argie Veroniki</t>
+          <t>Anders Sejr Hansen</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics, Associate Professor of Health Services, Policy and Practice</t>
+          <t>Assistant Professor of Biological Engineering Department</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>argie_veroniki@brown.edu</t>
+          <t>ashansen@mit.edu</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>statistical modeling for evidence synthesis; network meta-analysis; Individual Participant Data Meta-Analyses</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>A Critical Appraisal Tool for Individual Participant Data Meta-Analyses (CAT-IPDMA): Content Validity Assessment (2026)</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+          <t>super resolution microscopy; 3D genome architecture; chromatin looping</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://be.mit.edu/directory/anders-sejr-hansen</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -5207,49 +5147,57 @@
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ernest Fraenkel</t>
+          <t>Drew Beauchamp</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Neuroscience Institute</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Associate Professor of Biological Engineering Department</t>
+          <t>Assistant Professor, Neuroscience Institute, Biomedical Engineering</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>fraenkel-admin@mit.edu</t>
+          <t>jabeauchamp@cmu.edu</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>motor unit discharge; human-machine interfaces; motoneuron discharge</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Reverse engineering of motor unit discharge in multiple sclerosis reveals heterogeneity of voluntary motor commands (2026)</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>http://be.mit.edu/directory/ernest-fraenkel</t>
+          <t>https://beauchamplab.org/</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -5257,49 +5205,57 @@
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jeff Gore</t>
+          <t>Fatema Shafie Khorassani</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Boston University</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Associate Professor of Physics Department</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>gore@mit.edu</t>
+          <t>fshafie@bu.edu</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>statistical methods for surrogate endpoints; causal inference for observational data; survival analysis</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Continuous associations of the brief Wisconsin inventory of smoking dependence motives with transitions between cigarette and e-cigarette use (2026)</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>http://web.mit.edu/physics/people/faculty/gore_jeff.html</t>
+          <t>https://www.fatemashafie.com/</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -5307,48 +5263,44 @@
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Michael T. Hemann</t>
+          <t>Gopala Anumanchipalli</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>University of California Berkeley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Computational and Systems Biology</t>
+          <t>Neuroscience</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Associate Professor of Biology Department</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>hemann@mit.edu</t>
+          <t>gopala@eecs.berkeley.edu</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>informatics tools; loss of function genetic tools; combination chemotherapies</t>
-        </is>
-      </c>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://biology.mit.edu/people/michael_hemann</t>
+          <t>https://people.eecs.berkeley.edu/~gopala/</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5361,41 +5313,49 @@
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PhD Martina Pavlicova</t>
+          <t>Jonathan Tsay</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Neuroscience Institute</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics at the Columbia University Medical Center</t>
+          <t>Assistant Professor, Neuroscience Institute</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>mp2370@cumc.columbia.edu</t>
+          <t>jstsay@cmu.edu</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Large reaching datasets; Strategic Motor Learning; hidden dynamics of proprioception</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Tracking the hidden dynamics of proprioception (2026)</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
@@ -5407,17 +5367,17 @@
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PhD Cheng-Shiun Leu</t>
+          <t>Michele Santacatterina</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5427,18 +5387,26 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Associate Professor of Biostatistics (in Psychiatry) at CUMC</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>michele.santacatterina@nyulangone.org</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://michelesantacatterina.github.io</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>B</t>
@@ -5449,45 +5417,53 @@
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Abby Noyce</t>
+          <t>Stavroula Chrysanthopoulou</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Research Professor, Neuroscience Institute</t>
+          <t>Assistant Professor of Biostatistics, Director of the Master's Graduate Program in Biostatistics</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>anoyce@cmu.edu</t>
+          <t>stavroula_chrysanthopoulou@brown.edu</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>microsimulation modeling; complex predictive models applied in medical decision making; natural history of lung cancer</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Modeling Recurrent Events: A Tutorial Based on Relapse and Remitting Episodes during Medication-Assisted Treatment for Opioid Use Disorder (2025)</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -5495,47 +5471,43 @@
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>David R Gagnon</t>
+          <t>Eli Ben-Michael</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Research Professor</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>gagnon@bu.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor, joint with Heinz College</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>longitudinal data analysis; survival analysis; statistical computing</t>
+          <t>robust causal inference; data-driven decision making; statistical and computational methods</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Combined associations of GLP-1 receptor agonists and a healthy lifestyle with cardiovascular outcomes among individuals with type 2 diabetes: a prospective cohort study (2026)</t>
+          <t>Methodological considerations for investigating the impact of abortion restrictions on outcomes using aggregate panel data (2026)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5549,53 +5521,45 @@
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Kerrie P Nelson</t>
+          <t>Nina Lauharatanahirun</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Biostatistics</t>
+          <t>Center for Neural Engineering</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Research Professor</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>kerrie@bu.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor of Biomedical Engineering</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>assessing agreement in screening and diagnostic tests; probit hierarchical model; generalized linear mixed models</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Diagnostic accuracy analysis for multiple raters using probit hierarchical model for ordinal ratings (2025)</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://sites.psu.edu/decisionneurolab/</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -5603,50 +5567,42 @@
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Dave Touretzky</t>
+          <t>Rebecca Anthopolos</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Neuroscience Institute</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Research Professor, School of Computer Science, Neuroscience Institute and Robotics Institute</t>
+          <t>Assistant Professor, Department of Population Health</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Possible</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>artificial intelligence education; Neural Networks in Middle School; AI Elective</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Neural Networks in Middle School (2024)</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>http://www.cs.cmu.edu/~dst/</t>
-        </is>
-      </c>
+          <t>analysis of electronic health record data; sensitivity analysis; missing data assumptions</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>B</t>
@@ -5656,33 +5612,31 @@
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ankit Pensia</t>
+          <t>Soutrik Mandal</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>ankitp@cmu.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Possible</t>
@@ -5690,55 +5644,45 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>robust and heavy-tailed statistics; inference under constraints; Fast Algorithms for Sparse PCA and Robust Sparse Estimation</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Fast Algorithms for Sparse PCA and Robust Sparse Estimation (2026)</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>https://ankitp.net/</t>
-        </is>
-      </c>
+          <t>semiparametric and nonparametric methods in survival analysis; measurement error problems for high-dimensional data; parallel computing</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Weijing Tang</t>
+          <t>Yuki Oka</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>California Institute of Technology</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Computation and Neural Systems</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>weijingt@andrew.cmu.edu</t>
-        </is>
-      </c>
+          <t>Assistant Professor of Biology and Chen Scholar</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Possible</t>
@@ -5746,167 +5690,173 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>survival analysis; network analysis; Representation Learning with Blockwise Missingness; LLM Evaluation on Unseen Questions</t>
+          <t>Recovery of missing single-cell RNA-sequencing data; computational ethology; optimized transcriptomic references</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>LLM Evaluation on Unseen Questions: Contextual Multidimensional IRT Model (2026)</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/andrew.cmu.edu/weijingtang/home</t>
-        </is>
-      </c>
+          <t>Recovery of missing single-cell RNA-sequencing data with optimized transcriptomic references (2023)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Will Townes</t>
+          <t>Alice Paul</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Brown University</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor of Biostatistics Overview I am an Assosciate Professor of Biosta</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ftownes@andrew.cmu.edu</t>
+          <t>alice_paul@brown.edu</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>single cell RNA-Seq; spatial transcriptomics; dimension reduction</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>optimization algorithms underlying machine learning; variable selection; shared mobility systems</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Estimating Censored Spatial-Temporal Demand with Applications to Shared Micromobility (2023)</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://willtownes.github.io</t>
+          <t>http://alicepaul.github.io</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>2</v>
+      </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Yandi Shen</t>
+          <t>Christine Mauro</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>Associate Professor of Biostatistics at CUMC</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>yandis@andrew.cmu.edu</t>
+          <t>cmm2212@cumc.columbia.edu</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Poisson empirical Bayes estimation; Empirical Bayes linear regression in high dimensions; Approximate Message Passing with Random Initialization for Phase Retrieval</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Poisson empirical Bayes estimation: When does g-modeling beat f-modeling in theory (and in practice)? (2026)</t>
-        </is>
-      </c>
+          <t>statistical learning techniques; longitudinal data analysis; analysis of clinical trials</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://sayidshen.github.io/</t>
+          <t>https://christinemauro.com/</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Eli Ben-Michael</t>
+          <t>Linda Valeri</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Assistant Professor, joint with Heinz College</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Associate Professor of Biostatistics</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>lv2424@cumc.columbia.edu</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Possible</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>robust causal inference; data-driven decision making; statistical and computational methods</t>
+          <t>multistate approach; interventions on an intermediate time-to-event; health disparities research</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -5920,11 +5870,13 @@
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Arun Kumar Kuchibhotla</t>
+          <t>Mikael Kuusela</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5944,7 +5896,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>akuchibh@andrew.cmu.edu</t>
+          <t>mkuusela@andrew.cmu.edu</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5952,43 +5904,57 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>statistical learning in climate science; ill-posed inverse problems; uncertainty quantification</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Statistical Oceanography of Profiling Floats and Surface Drifters (2026)</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://www.stat.cmu.edu/~mkuusela/</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>2</v>
+      </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cosma Shalizi</t>
+          <t>Paul C. Blainey</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>Associate Professor of Biological Engineering Core Member, Broad Institute of Harvar</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>cshalizi@stat.cmu.edu</t>
+          <t>pblainey@broadinstitute.org</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5998,11 +5964,15 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>statistical inference for complex systems; nonparametric prediction for stochastic processes; causal inference; networks and information flow in neuroscience</t>
+          <t>cutting-edge microfluidic, molecular, and optical methods; reliable, high-quality data; throughput of biological experimentation</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://be.mit.edu/directory/paul-blainey</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>B</t>
@@ -6012,31 +5982,33 @@
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>2</v>
+      </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>David Choi</t>
+          <t>Tami Lieberman</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Computational and Systems Biology</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Associate Professor of Statistics and Information Systems</t>
+          <t>Associate Professor of Institute for Medical Engineering and Science &amp; Civil and Env</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>davidch@andrew.cmu.edu</t>
+          <t>tami@mit.edu</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6046,55 +6018,49 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>machine learning for network data; community detection; causal inference; Agnostic Characterization of Interference in Randomized Experiments</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Agnostic Characterization of Interference in Randomized Experiments (2024)</t>
-        </is>
-      </c>
+          <t>human microbiome; selective pressures they face; niche ranges</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>http://www.andrew.cmu.edu/user/davidch/</t>
+          <t>https://imes.mit.edu/people/faculty/tami-lieberman/</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mikael Kuusela</t>
+          <t>Hanga Galfalvy</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Department of Statistics &amp; Data Science</t>
+          <t>Biostatistics</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>mkuusela@andrew.cmu.edu</t>
-        </is>
-      </c>
+          <t>Associate Professor of Biostatistics (in Psychiatry) at CUMC</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -6102,15 +6068,11 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>statistical learning in climate science; ill-posed inverse problems; uncertainty quantification</t>
+          <t>prediction models for suicide; statistical genetics; analysis of multidimensional longitudinally measured data</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>https://www.stat.cmu.edu/~mkuusela/</t>
-        </is>
-      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>B</t>
@@ -6120,11 +6082,13 @@
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Nynke Niezink</t>
+          <t>Vibha Viswanathan</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6134,48 +6098,994 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>Neuroscience Institute</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Research Scientist (Special Faculty), Neuroscience Institute</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>vibhavis@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Auditory Scene Analysis; Induced alpha and beta electroencephalographic rhythms; single-trial speech intelligibility</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Prediction from Statistical Learning Aids Auditory Scene Analysis (2026)</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Anarina Murillo</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Brown University</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Biostatistics</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>anarina_murillo@brown.edu</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>statistics education; measurement error; longitudinal data</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>A comparison of methods for coding race in linear and logistic regression models (2025)</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>https://www.anarinalm.com/</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Bryan Bryson</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Computational and Systems Biology</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Biological Engineering Department</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>bryand@mit.edu</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>dynamics of bacterial infection; quantitative modeling; reverse-engineering a vaccine for tuberculosis</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://csbphd.mit.edu/faculty_spotlight/bryson/</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Francisco J. Sánchez-Rivera</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Computational and Systems Biology</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Biology</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>fsr@mit.edu</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>genetic variation shapes normal physiology and disease; with a focus on cancer; normal physiology</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>https://biology.mit.edu/profile/francisco-j-sanchez-rivera/</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Kevin M. Esvelt</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Computational and Systems Biology</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Media Arts and Science NEC Career Development Professor of Co</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>esvelt@mit.edu</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>http://www.sculptingevolution.org/</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Sossena Wood</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Neuroscience Institute</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Biomedical Engineering and Neuroscience Institute</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>scwood@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Computational Fluid Dynamics; Patient-Specific Modeling; Central Sensitization</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Computational Fluid Dynamics Analysis of Cerebrovascular Hemodynamic Differences in Adults with Sickle Cell Disease: Comparing Stroke and Non-Stroke Cohorts (2026)</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>https://www.sossenawood.com/</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Xiaoyu Che</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Columbia University</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Assistant Professor of Biostatistics (In the Center for Infection and Immunity) at CUMC</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>xc2273@cumc.columbia.edu</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://www.publichealth.columbia.edu/research/faculty-research-labs-programs</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Hakhamanesh Mostafavi</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Assistant Professor, Department of Population Health, Affiliation: Center for Human Genetics &amp; Genomics</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Possible</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Argie Veroniki</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Brown University</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Associate Professor of Biostatistics, Associate Professor of Health Services, Policy and Practice</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>argie_veroniki@brown.edu</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>statistical modeling for evidence synthesis; network meta-analysis; Individual Participant Data Meta-Analyses</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>A Critical Appraisal Tool for Individual Participant Data Meta-Analyses (CAT-IPDMA): Content Validity Assessment (2026)</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Arun Kumar Kuchibhotla</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>Department of Statistics &amp; Data Science</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>Associate Professor</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>nynke@stat.cmu.edu</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>akuchibh@andrew.cmu.edu</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>statistical inference for social network data; relational event models; multiplex networks</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Cognitive and Behavioral Perspectives on Social Network Agency (2026)</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>http://www.stat.cmu.edu/~nynke/</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Generalized Asymptotic Limit Theory and Inference for Isotonic Regression (2026)</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Michael T. Hemann</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Computational and Systems Biology</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Associate Professor of Biology Department</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>hemann@mit.edu</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>informatics tools; loss of function genetic tools; combination chemotherapies</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>https://biology.mit.edu/people/michael_hemann</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Vladimir Itskov</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pennsylvania State University</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Center for Neural Engineering</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Associate Professor of Mathematics</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>vladimir.itskov@psu.edu</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>https://vitskov.github.io/homepage/</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Aida Ebrahimi</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pennsylvania State University</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Center for Neural Engineering</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Thomas and Sheila Roell Early Career Associate Professor</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>https://blockchain.cse.psu.edu/</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Cheng-Shiun Leu</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Columbia University</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Associate Professor of Biostatistics (in Psychiatry) at CUMC</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Jacob M Schauer</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Northwestern University</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Associate Professor, Preventive Medicine (Biostatistics and Informatics)</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Samrachana Adhikari</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Associate Professor, Department of Population Health</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>David R Gagnon</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Boston University</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Research Professor</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>gagnon@bu.edu</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>longitudinal data analysis; survival analysis; statistical computing</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Combined associations of GLP-1 receptor agonists and a healthy lifestyle with cardiovascular outcomes among individuals with type 2 diabetes: a prospective cohort study (2026)</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Kerrie P Nelson</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Boston University</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Research Professor</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>kerrie@bu.edu</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>assessing agreement in screening and diagnostic tests; probit hierarchical model; generalized linear mixed models</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Diagnostic accuracy analysis for multiple raters using probit hierarchical model for ordinal ratings (2025)</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Carole Siegel</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Biostatistics</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Research Professor, Departments of Psychiatry and Population Health</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Dave Touretzky</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Neuroscience Institute</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Research Professor, School of Computer Science, Neuroscience Institute and Robotics Institute</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>artificial intelligence education; Neural Networks in Middle School; AI Elective</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Neural Networks in Middle School (2024)</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>http://www.cs.cmu.edu/~dst/</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N103"/>
+  <autoFilter ref="A1:N122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>